--- a/進行/テキスト/GameText.xlsx
+++ b/進行/テキスト/GameText.xlsx
@@ -7,7 +7,8 @@
     <sheet name="2章" sheetId="3" r:id="rId3"/>
     <sheet name="3章" sheetId="4" r:id="rId4"/>
     <sheet name="終章" sheetId="5" r:id="rId5"/>
-    <sheet name="共通" sheetId="6" r:id="rId6"/>
+    <sheet name="拾得" sheetId="6" r:id="rId6"/>
+    <sheet name="共通" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -179,6 +180,11 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">新聞記事</t>
@@ -242,12 +248,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/dim.flashlight.name</t>
+          <t xml:space="preserve">doc/dim.toy.title</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc</t>
+          <t xml:space="preserve">toy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -262,19 +268,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">懐中電灯</t>
+          <t xml:space="preserve">思い出の断片：木のガラガラ</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/dim.flashlight.hint</t>
+          <t xml:space="preserve">doc/dim.toy.body</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc</t>
+          <t xml:space="preserve">toy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -289,24 +295,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">F: 点灯</t>
+          <t xml:space="preserve">@file:doc_dim.toy.body</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/dim.notebook.name</t>
+          <t xml:space="preserve">room/train.name</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc</t>
+          <t xml:space="preserve">room</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">dim</t>
+          <t xml:space="preserve">train</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -316,24 +322,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">手帳</t>
+          <t xml:space="preserve">電車車内</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/dim.notebook.hint</t>
+          <t xml:space="preserve">room/train.chapter</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc</t>
+          <t xml:space="preserve">room</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">dim</t>
+          <t xml:space="preserve">train</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -343,24 +349,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tab: 開く</t>
+          <t xml:space="preserve">チュートリアル　2節</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/dim.toy.name</t>
+          <t xml:space="preserve">doc/train.ad.name</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">doc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">dim</t>
+          <t xml:space="preserve">train</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -368,26 +374,31 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">木のガラガラ</t>
+          <t xml:space="preserve">中吊り広告</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/dim.toy.title</t>
+          <t xml:space="preserve">doc/train.ad.title</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">doc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dim</t>
+          <t xml:space="preserve">train</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -397,24 +408,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">思い出の断片：木のガラガラ</t>
+          <t xml:space="preserve">中吊り広告</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/dim.toy.body</t>
+          <t xml:space="preserve">doc/train.ad.body</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">doc</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">dim</t>
+          <t xml:space="preserve">train</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -424,14 +435,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:doc_dim.toy.body</t>
+          <t xml:space="preserve">@file:doc_train.ad.body</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/dim.toy.hint</t>
+          <t xml:space="preserve">doc/train.toy.title</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -441,7 +452,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">dim</t>
+          <t xml:space="preserve">train</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -451,19 +462,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">娘の記憶</t>
+          <t xml:space="preserve">思い出の断片：うさぎのぬいぐるみ</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">room/train.name</t>
+          <t xml:space="preserve">doc/train.toy.body</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">room</t>
+          <t xml:space="preserve">toy</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -478,14 +489,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">電車車内</t>
+          <t xml:space="preserve">@file:doc_train.toy.body</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">room/train.chapter</t>
+          <t xml:space="preserve">room/lab.name</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -495,7 +506,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">train</t>
+          <t xml:space="preserve">lab</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -505,24 +516,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">チュートリアル　2節</t>
+          <t xml:space="preserve">研究所応接室</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/train.ad.name</t>
+          <t xml:space="preserve">room/lab.chapter</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc</t>
+          <t xml:space="preserve">room</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">train</t>
+          <t xml:space="preserve">lab</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -532,14 +543,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">中吊り広告</t>
+          <t xml:space="preserve">チュートリアル　3節</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/train.ad.title</t>
+          <t xml:space="preserve">doc/lab.summary.name</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -549,7 +560,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">train</t>
+          <t xml:space="preserve">lab</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -557,16 +568,21 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">中吊り広告</t>
+          <t xml:space="preserve">研究概要</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/train.ad.body</t>
+          <t xml:space="preserve">doc/lab.summary.title</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -576,7 +592,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">train</t>
+          <t xml:space="preserve">lab</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -586,24 +602,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:doc_train.ad.body</t>
+          <t xml:space="preserve">研究概要</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/train.toy.name</t>
+          <t xml:space="preserve">doc/lab.summary.body</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">doc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">train</t>
+          <t xml:space="preserve">lab</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -613,24 +629,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">うさぎのぬいぐるみ</t>
+          <t xml:space="preserve">@file:doc_lab.summary.body</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/train.toy.title</t>
+          <t xml:space="preserve">doc/lab.members.name</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">doc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">train</t>
+          <t xml:space="preserve">lab</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -638,26 +654,31 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">思い出の断片：うさぎのぬいぐるみ</t>
+          <t xml:space="preserve">社員名簿</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/train.toy.body</t>
+          <t xml:space="preserve">doc/lab.members.title</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">doc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">train</t>
+          <t xml:space="preserve">lab</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -667,24 +688,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:doc_train.toy.body</t>
+          <t xml:space="preserve">社員名簿</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/train.toy.hint</t>
+          <t xml:space="preserve">doc/lab.members.body</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">doc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">train</t>
+          <t xml:space="preserve">lab</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -694,19 +715,19 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">娘の記憶</t>
+          <t xml:space="preserve">@file:doc_lab.members.body</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">room/lab.name</t>
+          <t xml:space="preserve">doc/lab.toy.title</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">room</t>
+          <t xml:space="preserve">toy</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -721,19 +742,19 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">研究所応接室</t>
+          <t xml:space="preserve">思い出の断片：折り紙の鶴</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">room/lab.chapter</t>
+          <t xml:space="preserve">doc/lab.toy.body</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">room</t>
+          <t xml:space="preserve">toy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -748,277 +769,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">チュートリアル　3節</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">doc/lab.summary.name</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">doc</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lab</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仮</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">研究概要</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">doc/lab.summary.title</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">doc</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lab</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仮</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">研究概要</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">doc/lab.summary.body</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">doc</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lab</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仮</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">@file:doc_lab.summary.body</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">doc/lab.members.name</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">doc</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lab</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仮</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">社員名簿</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">doc/lab.members.title</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">doc</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lab</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仮</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">社員名簿</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">doc/lab.members.body</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">doc</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lab</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仮</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">@file:doc_lab.members.body</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">doc/lab.toy.name</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">toy</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lab</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仮</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">折り紙の鶴</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">doc/lab.toy.title</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">toy</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lab</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仮</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">思い出の断片：折り紙の鶴</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">doc/lab.toy.body</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">toy</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lab</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仮</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
           <t xml:space="preserve">@file:doc_lab.toy.body</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">doc/lab.toy.hint</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">toy</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lab</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仮</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">娘の記憶</t>
         </is>
       </c>
     </row>
@@ -1156,6 +907,11 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">文書</t>
@@ -1237,6 +993,11 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">手帳の切れ端</t>
@@ -1318,6 +1079,11 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">封書</t>
@@ -1399,6 +1165,11 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">伏せられた写真立て</t>
@@ -1462,7 +1233,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/study.toy.name</t>
+          <t xml:space="preserve">doc/study.toy.title</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1482,14 +1253,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">絵本『おやすみ』</t>
+          <t xml:space="preserve">思い出の断片：絵本『おやすみ』</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/study.toy.title</t>
+          <t xml:space="preserve">doc/study.toy.body</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1509,19 +1280,19 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">思い出の断片：絵本『おやすみ』</t>
+          <t xml:space="preserve">@file:doc_study.toy.body</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/study.toy.body</t>
+          <t xml:space="preserve">echo/study_secret.title</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">echo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1536,19 +1307,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:doc_study.toy.body</t>
+          <t xml:space="preserve">残響：主任と佐伯の密談（私の記憶）</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/study.toy.hint</t>
+          <t xml:space="preserve">echo/study_secret.body</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">echo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1563,19 +1334,19 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">娘の記憶</t>
+          <t xml:space="preserve">@file:echo_study_secret.body</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">echo/study_secret.title</t>
+          <t xml:space="preserve">lock/study.safekey.name</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">echo</t>
+          <t xml:space="preserve">lock</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1590,19 +1361,19 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">残響：主任と佐伯の密談（私の記憶）</t>
+          <t xml:space="preserve">壁の金庫</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">echo/study_secret.body</t>
+          <t xml:space="preserve">lock/study.safekey.success_title</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">echo</t>
+          <t xml:space="preserve">lock</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1617,14 +1388,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:echo_study_secret.body</t>
+          <t xml:space="preserve">金庫の中身：解析室キャビネットの鍵</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/study.safekey.name</t>
+          <t xml:space="preserve">lock/study.safekey.success_body</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1644,14 +1415,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">壁の金庫</t>
+          <t xml:space="preserve">@file:lock_study.safekey.success_body</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/study.safekey.success_title</t>
+          <t xml:space="preserve">lock/study.safekey.require</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1671,14 +1442,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">金庫の中身：解析室キャビネットの鍵</t>
+          <t xml:space="preserve">まだ、必要なものが揃っていない。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/study.safekey.success_body</t>
+          <t xml:space="preserve">lock/study.safekey.title</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1698,14 +1469,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:lock_study.safekey.success_body</t>
+          <t xml:space="preserve">金庫のダイヤル</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/study.safekey.require</t>
+          <t xml:space="preserve">lock/study.safekey.body</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1725,24 +1496,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">まだ、必要なものが揃っていない。</t>
+          <t xml:space="preserve">@file:lock_study.safekey.body</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/study.safekey.title</t>
+          <t xml:space="preserve">room/analysis.name</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock</t>
+          <t xml:space="preserve">room</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">study</t>
+          <t xml:space="preserve">analysis</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1752,24 +1523,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">金庫のダイヤル</t>
+          <t xml:space="preserve">脳神経解析室</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/study.safekey.body</t>
+          <t xml:space="preserve">room/analysis.chapter</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock</t>
+          <t xml:space="preserve">room</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">study</t>
+          <t xml:space="preserve">analysis</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1779,19 +1550,19 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:lock_study.safekey.body</t>
+          <t xml:space="preserve">1章『佐伯恒一』　─ 転 ─</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">room/analysis.name</t>
+          <t xml:space="preserve">doc/analysis.helmet.name</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">room</t>
+          <t xml:space="preserve">doc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1804,21 +1575,26 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">脳神経解析室</t>
+          <t xml:space="preserve">ヘルメット型スキャン装置</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">room/analysis.chapter</t>
+          <t xml:space="preserve">doc/analysis.helmet.title</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">room</t>
+          <t xml:space="preserve">doc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1833,14 +1609,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1章『佐伯恒一』　─ 転 ─</t>
+          <t xml:space="preserve">ヘルメット型スキャン装置</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/analysis.helmet.name</t>
+          <t xml:space="preserve">doc/analysis.helmet.body</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1860,14 +1636,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルメット型スキャン装置</t>
+          <t xml:space="preserve">@file:doc_analysis.helmet.body</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/analysis.helmet.title</t>
+          <t xml:space="preserve">doc/analysis.idcard.name</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1885,16 +1661,21 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルメット型スキャン装置</t>
+          <t xml:space="preserve">職員証</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/analysis.helmet.body</t>
+          <t xml:space="preserve">doc/analysis.idcard.title</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1914,14 +1695,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:doc_analysis.helmet.body</t>
+          <t xml:space="preserve">職員証（佐伯恒一）</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/analysis.idcard.name</t>
+          <t xml:space="preserve">doc/analysis.idcard.body</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1941,14 +1722,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">職員証</t>
+          <t xml:space="preserve">@file:doc_analysis.idcard.body</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/analysis.idcard.title</t>
+          <t xml:space="preserve">doc/analysis.plan.name</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1966,16 +1747,21 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">職員証（佐伯恒一）</t>
+          <t xml:space="preserve">研究計画書</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/analysis.idcard.body</t>
+          <t xml:space="preserve">doc/analysis.plan.title</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1995,14 +1781,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:doc_analysis.idcard.body</t>
+          <t xml:space="preserve">リナシータ研究計画書</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/analysis.plan.name</t>
+          <t xml:space="preserve">doc/analysis.plan.body</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2022,14 +1808,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">研究計画書</t>
+          <t xml:space="preserve">@file:doc_analysis.plan.body</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/analysis.plan.title</t>
+          <t xml:space="preserve">doc/analysis.spec.name</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2047,16 +1833,21 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">リナシータ研究計画書</t>
+          <t xml:space="preserve">アルゴリズム仕様</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/analysis.plan.body</t>
+          <t xml:space="preserve">doc/analysis.spec.title</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2076,14 +1867,14 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:doc_analysis.plan.body</t>
+          <t xml:space="preserve">補完アルゴリズム仕様（佐伯）</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/analysis.spec.name</t>
+          <t xml:space="preserve">doc/analysis.spec.body</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2103,14 +1894,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">アルゴリズム仕様</t>
+          <t xml:space="preserve">@file:doc_analysis.spec.body</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/analysis.spec.title</t>
+          <t xml:space="preserve">doc/analysis.anomaly.name</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2128,16 +1919,21 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">補完アルゴリズム仕様（佐伯）</t>
+          <t xml:space="preserve">異常レポート</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/analysis.spec.body</t>
+          <t xml:space="preserve">doc/analysis.anomaly.title</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2157,14 +1953,14 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:doc_analysis.spec.body</t>
+          <t xml:space="preserve">異常レポート（佐伯→所長）</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/analysis.anomaly.name</t>
+          <t xml:space="preserve">doc/analysis.anomaly.body</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2184,19 +1980,19 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">異常レポート</t>
+          <t xml:space="preserve">@file:doc_analysis.anomaly.body</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/analysis.anomaly.title</t>
+          <t xml:space="preserve">doc/analysis.toy.title</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc</t>
+          <t xml:space="preserve">toy</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2211,19 +2007,19 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">異常レポート（佐伯→所長）</t>
+          <t xml:space="preserve">思い出の断片：おもちゃの聴診器</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/analysis.anomaly.body</t>
+          <t xml:space="preserve">doc/analysis.toy.body</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc</t>
+          <t xml:space="preserve">toy</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2238,19 +2034,19 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:doc_analysis.anomaly.body</t>
+          <t xml:space="preserve">@file:doc_analysis.toy.body</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/analysis.toy.name</t>
+          <t xml:space="preserve">lock/analysis.circuit.name</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">lock</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2265,19 +2061,19 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">おもちゃの聴診器</t>
+          <t xml:space="preserve">記憶回路端末</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/analysis.toy.title</t>
+          <t xml:space="preserve">lock/analysis.circuit.success_title</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">lock</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2292,19 +2088,19 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">思い出の断片：おもちゃの聴診器</t>
+          <t xml:space="preserve">記憶回路：補完テスト成功</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/analysis.toy.body</t>
+          <t xml:space="preserve">lock/analysis.circuit.success_body</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">lock</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2319,19 +2115,19 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:doc_analysis.toy.body</t>
+          <t xml:space="preserve">@file:lock_analysis.circuit.success_body</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/analysis.toy.hint</t>
+          <t xml:space="preserve">lock/analysis.circuit.require</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">lock</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2346,14 +2142,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">娘の記憶</t>
+          <t xml:space="preserve">まだ、必要なものが揃っていない。</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/analysis.circuit.name</t>
+          <t xml:space="preserve">lock/analysis.circuit.title</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2373,14 +2169,14 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">記憶回路端末</t>
+          <t xml:space="preserve">記憶回路　── 補完テスト ──</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/analysis.circuit.success_title</t>
+          <t xml:space="preserve">lock/analysis.circuit.body</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2400,24 +2196,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">記憶回路：補完テスト成功</t>
+          <t xml:space="preserve">@file:lock_analysis.circuit.body</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/analysis.circuit.success_body</t>
+          <t xml:space="preserve">room/saeki_home.name</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock</t>
+          <t xml:space="preserve">room</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">analysis</t>
+          <t xml:space="preserve">saeki_home</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2427,24 +2223,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:lock_analysis.circuit.success_body</t>
+          <t xml:space="preserve">佐伯の自宅</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/analysis.circuit.require</t>
+          <t xml:space="preserve">room/saeki_home.chapter</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock</t>
+          <t xml:space="preserve">room</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">analysis</t>
+          <t xml:space="preserve">saeki_home</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2454,24 +2250,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">まだ、必要なものが揃っていない。</t>
+          <t xml:space="preserve">1章『佐伯恒一』　─ 結 ─</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/analysis.circuit.title</t>
+          <t xml:space="preserve">doc/saeki_home.letter.name</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock</t>
+          <t xml:space="preserve">doc</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">analysis</t>
+          <t xml:space="preserve">saeki_home</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2479,26 +2275,31 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">記憶回路　── 補完テスト ──</t>
+          <t xml:space="preserve">書きかけの手紙</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/analysis.circuit.body</t>
+          <t xml:space="preserve">doc/saeki_home.letter.title</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock</t>
+          <t xml:space="preserve">doc</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">analysis</t>
+          <t xml:space="preserve">saeki_home</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2508,19 +2309,19 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:lock_analysis.circuit.body</t>
+          <t xml:space="preserve">妻の書きかけの手紙</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">room/saeki_home.name</t>
+          <t xml:space="preserve">doc/saeki_home.letter.body</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">room</t>
+          <t xml:space="preserve">doc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2535,19 +2336,19 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">佐伯の自宅</t>
+          <t xml:space="preserve">@file:doc_saeki_home.letter.body</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">room/saeki_home.chapter</t>
+          <t xml:space="preserve">doc/saeki_home.plog.name</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">room</t>
+          <t xml:space="preserve">doc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2560,16 +2361,21 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1章『佐伯恒一』　─ 結 ─</t>
+          <t xml:space="preserve">私的ログ</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/saeki_home.letter.name</t>
+          <t xml:space="preserve">doc/saeki_home.plog.title</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2589,14 +2395,14 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">書きかけの手紙</t>
+          <t xml:space="preserve">佐伯の私的ログ（最終頁）</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/saeki_home.letter.title</t>
+          <t xml:space="preserve">doc/saeki_home.plog.body</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2616,14 +2422,14 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">妻の書きかけの手紙</t>
+          <t xml:space="preserve">@file:doc_saeki_home.plog.body</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/saeki_home.letter.body</t>
+          <t xml:space="preserve">doc/saeki_home.unsent.name</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2641,16 +2447,21 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:doc_saeki_home.letter.body</t>
+          <t xml:space="preserve">未送信メモ</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/saeki_home.plog.name</t>
+          <t xml:space="preserve">doc/saeki_home.unsent.title</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2670,14 +2481,14 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">私的ログ</t>
+          <t xml:space="preserve">宛先のないメモ</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/saeki_home.plog.title</t>
+          <t xml:space="preserve">doc/saeki_home.unsent.body</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2697,19 +2508,19 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">佐伯の私的ログ（最終頁）</t>
+          <t xml:space="preserve">@file:doc_saeki_home.unsent.body</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/saeki_home.plog.body</t>
+          <t xml:space="preserve">doc/saeki_home.toy.title</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc</t>
+          <t xml:space="preserve">toy</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2724,19 +2535,19 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:doc_saeki_home.plog.body</t>
+          <t xml:space="preserve">思い出の断片：ままごとのカップ</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/saeki_home.unsent.name</t>
+          <t xml:space="preserve">doc/saeki_home.toy.body</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc</t>
+          <t xml:space="preserve">toy</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2751,19 +2562,19 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">未送信メモ</t>
+          <t xml:space="preserve">@file:doc_saeki_home.toy.body</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/saeki_home.unsent.title</t>
+          <t xml:space="preserve">echo/argue_saeki.title</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc</t>
+          <t xml:space="preserve">echo</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2778,19 +2589,19 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">宛先のないメモ</t>
+          <t xml:space="preserve">残響：口論（佐伯の記憶）</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/saeki_home.unsent.body</t>
+          <t xml:space="preserve">echo/argue_saeki.body</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc</t>
+          <t xml:space="preserve">echo</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2805,19 +2616,19 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:doc_saeki_home.unsent.body</t>
+          <t xml:space="preserve">@file:echo_argue_saeki.body</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/saeki_home.toy.name</t>
+          <t xml:space="preserve">echo/saeki_wife.title</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">echo</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2832,19 +2643,19 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">ままごとのカップ</t>
+          <t xml:space="preserve">残響：二人分の食器（妻の記憶）</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/saeki_home.toy.title</t>
+          <t xml:space="preserve">echo/saeki_wife.body</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">echo</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2858,168 +2669,6 @@
         </is>
       </c>
       <c r="G67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">思い出の断片：ままごとのカップ</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">doc/saeki_home.toy.body</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">toy</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">saeki_home</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仮</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">@file:doc_saeki_home.toy.body</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">doc/saeki_home.toy.hint</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">toy</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">saeki_home</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仮</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">娘の記憶</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">echo/argue_saeki.title</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">echo</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">saeki_home</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仮</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">残響：口論（佐伯の記憶）</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">echo/argue_saeki.body</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">echo</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">saeki_home</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仮</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">@file:echo_argue_saeki.body</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">echo/saeki_wife.title</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">echo</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">saeki_home</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仮</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">残響：二人分の食器（妻の記憶）</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">echo/saeki_wife.body</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">echo</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">saeki_home</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仮</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
         <is>
           <t xml:space="preserve">@file:echo_saeki_wife.body</t>
         </is>
@@ -3159,6 +2808,11 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">観察記録</t>
@@ -3240,6 +2894,11 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">少女のファイル</t>
@@ -3303,7 +2962,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/ward.toy.name</t>
+          <t xml:space="preserve">doc/ward.toy.title</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3323,14 +2982,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">紙の王冠</t>
+          <t xml:space="preserve">思い出の断片：紙の王冠</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/ward.toy.title</t>
+          <t xml:space="preserve">doc/ward.toy.body</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3350,19 +3009,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">思い出の断片：紙の王冠</t>
+          <t xml:space="preserve">@file:doc_ward.toy.body</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/ward.toy.body</t>
+          <t xml:space="preserve">echo/talk_me.title</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">echo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3377,19 +3036,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:doc_ward.toy.body</t>
+          <t xml:space="preserve">残響：会話（私の記憶）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/ward.toy.hint</t>
+          <t xml:space="preserve">echo/talk_me.body</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">echo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3404,24 +3063,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">娘の記憶</t>
+          <t xml:space="preserve">@file:echo_talk_me.body</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">echo/talk_me.title</t>
+          <t xml:space="preserve">room/core_ante.name</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">echo</t>
+          <t xml:space="preserve">room</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ward</t>
+          <t xml:space="preserve">core_ante</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3431,24 +3090,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">残響：会話（私の記憶）</t>
+          <t xml:space="preserve">CORE前室</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">echo/talk_me.body</t>
+          <t xml:space="preserve">room/core_ante.chapter</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">echo</t>
+          <t xml:space="preserve">room</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ward</t>
+          <t xml:space="preserve">core_ante</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3458,19 +3117,19 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:echo_talk_me.body</t>
+          <t xml:space="preserve">2章『水野美奈』　─ 転 ─</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">room/core_ante.name</t>
+          <t xml:space="preserve">doc/core_ante.manual.name</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">room</t>
+          <t xml:space="preserve">doc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3483,21 +3142,26 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORE前室</t>
+          <t xml:space="preserve">運用手順書</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">room/core_ante.chapter</t>
+          <t xml:space="preserve">doc/core_ante.manual.title</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">room</t>
+          <t xml:space="preserve">doc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3512,14 +3176,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2章『水野美奈』　─ 転 ─</t>
+          <t xml:space="preserve">リナシータ運用手順書</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/core_ante.manual.name</t>
+          <t xml:space="preserve">doc/core_ante.manual.body</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3539,14 +3203,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">運用手順書</t>
+          <t xml:space="preserve">@file:doc_core_ante.manual.body</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/core_ante.manual.title</t>
+          <t xml:space="preserve">doc/core_ante.brainlist.name</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3564,16 +3228,21 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">リナシータ運用手順書</t>
+          <t xml:space="preserve">登録一覧</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/core_ante.manual.body</t>
+          <t xml:space="preserve">doc/core_ante.brainlist.title</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3593,14 +3262,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:doc_core_ante.manual.body</t>
+          <t xml:space="preserve">BRAIN DATA 登録一覧</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/core_ante.brainlist.name</t>
+          <t xml:space="preserve">doc/core_ante.brainlist.body</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3620,14 +3289,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">登録一覧</t>
+          <t xml:space="preserve">@file:doc_core_ante.brainlist.body</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/core_ante.brainlist.title</t>
+          <t xml:space="preserve">doc/core_ante.wmemo.name</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3645,16 +3314,21 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRAIN DATA 登録一覧</t>
+          <t xml:space="preserve">発見メモ</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/core_ante.brainlist.body</t>
+          <t xml:space="preserve">doc/core_ante.wmemo.title</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3674,14 +3348,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:doc_core_ante.brainlist.body</t>
+          <t xml:space="preserve">水野の発見メモ</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/core_ante.wmemo.name</t>
+          <t xml:space="preserve">doc/core_ante.wmemo.body</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3701,14 +3375,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">発見メモ</t>
+          <t xml:space="preserve">@file:doc_core_ante.wmemo.body</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/core_ante.wmemo.title</t>
+          <t xml:space="preserve">doc/core_ante.unsentmsg.name</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3726,16 +3400,21 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">水野の発見メモ</t>
+          <t xml:space="preserve">未送信メッセージ</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/core_ante.wmemo.body</t>
+          <t xml:space="preserve">doc/core_ante.unsentmsg.title</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3755,14 +3434,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:doc_core_ante.wmemo.body</t>
+          <t xml:space="preserve">未送信メッセージ（水野）</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/core_ante.unsentmsg.name</t>
+          <t xml:space="preserve">doc/core_ante.unsentmsg.body</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3782,19 +3461,19 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">未送信メッセージ</t>
+          <t xml:space="preserve">@file:doc_core_ante.unsentmsg.body</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/core_ante.unsentmsg.title</t>
+          <t xml:space="preserve">doc/core_ante.toy.title</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc</t>
+          <t xml:space="preserve">toy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3809,19 +3488,19 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">未送信メッセージ（水野）</t>
+          <t xml:space="preserve">思い出の断片：ビー玉</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/core_ante.unsentmsg.body</t>
+          <t xml:space="preserve">doc/core_ante.toy.body</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc</t>
+          <t xml:space="preserve">toy</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3836,19 +3515,19 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:doc_core_ante.unsentmsg.body</t>
+          <t xml:space="preserve">@file:doc_core_ante.toy.body</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/core_ante.toy.name</t>
+          <t xml:space="preserve">lock/core_ante.power.name</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">lock</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3863,19 +3542,19 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビー玉</t>
+          <t xml:space="preserve">配電盤</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/core_ante.toy.title</t>
+          <t xml:space="preserve">lock/core_ante.power.success_title</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">lock</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3890,19 +3569,19 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">思い出の断片：ビー玉</t>
+          <t xml:space="preserve">配電盤：系統復電 完了</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/core_ante.toy.body</t>
+          <t xml:space="preserve">lock/core_ante.power.success_body</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">lock</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3917,19 +3596,19 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:doc_core_ante.toy.body</t>
+          <t xml:space="preserve">@file:lock_core_ante.power.success_body</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/core_ante.toy.hint</t>
+          <t xml:space="preserve">lock/core_ante.power.require</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">lock</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3944,14 +3623,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">娘の記憶</t>
+          <t xml:space="preserve">まだ、必要なものが揃っていない。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/core_ante.power.name</t>
+          <t xml:space="preserve">lock/core_ante.power.title</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3971,14 +3650,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">配電盤</t>
+          <t xml:space="preserve">配電盤　── 系統別給電 ──</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/core_ante.power.success_title</t>
+          <t xml:space="preserve">lock/core_ante.power.body</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3998,14 +3677,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">配電盤：系統復電 完了</t>
+          <t xml:space="preserve">非常電源から各系統へ復電する。給電する系統を順に選ぶこと。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/core_ante.power.success_body</t>
+          <t xml:space="preserve">lock/core_ante.power.step.0</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4025,14 +3704,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:lock_core_ante.power.success_body</t>
+          <t xml:space="preserve">言語野</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/core_ante.power.require</t>
+          <t xml:space="preserve">lock/core_ante.power.step.1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4052,14 +3731,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">まだ、必要なものが揃っていない。</t>
+          <t xml:space="preserve">自己認識野</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/core_ante.power.title</t>
+          <t xml:space="preserve">lock/core_ante.power.step.2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4079,24 +3758,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">配電盤　── 系統別給電 ──</t>
+          <t xml:space="preserve">記憶野</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/core_ante.power.body</t>
+          <t xml:space="preserve">room/mizuno_apart.name</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock</t>
+          <t xml:space="preserve">room</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">core_ante</t>
+          <t xml:space="preserve">mizuno_apart</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4106,24 +3785,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">非常電源から各系統へ復電する。給電する系統を順に選ぶこと。</t>
+          <t xml:space="preserve">水野のアパート</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/core_ante.power.step.0</t>
+          <t xml:space="preserve">room/mizuno_apart.chapter</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock</t>
+          <t xml:space="preserve">room</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">core_ante</t>
+          <t xml:space="preserve">mizuno_apart</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4133,24 +3812,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">言語野</t>
+          <t xml:space="preserve">2章『水野美奈』　─ 結 ─</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/core_ante.power.step.1</t>
+          <t xml:space="preserve">doc/mizuno_apart.diary.name</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock</t>
+          <t xml:space="preserve">doc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">core_ante</t>
+          <t xml:space="preserve">mizuno_apart</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4158,26 +3837,31 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">自己認識野</t>
+          <t xml:space="preserve">日記帳</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/core_ante.power.step.2</t>
+          <t xml:space="preserve">doc/mizuno_apart.diary.title</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock</t>
+          <t xml:space="preserve">doc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">core_ante</t>
+          <t xml:space="preserve">mizuno_apart</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4187,19 +3871,19 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">記憶野</t>
+          <t xml:space="preserve">水野の日記</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">room/mizuno_apart.name</t>
+          <t xml:space="preserve">doc/mizuno_apart.diary.body</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">room</t>
+          <t xml:space="preserve">doc</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4214,19 +3898,19 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">水野のアパート</t>
+          <t xml:space="preserve">@file:doc_mizuno_apart.diary.body</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">room/mizuno_apart.chapter</t>
+          <t xml:space="preserve">doc/mizuno_apart.recorder.name</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">room</t>
+          <t xml:space="preserve">doc</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4239,16 +3923,21 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2章『水野美奈』　─ 結 ─</t>
+          <t xml:space="preserve">ボイスレコーダー</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/mizuno_apart.diary.name</t>
+          <t xml:space="preserve">doc/mizuno_apart.recorder.title</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4268,14 +3957,14 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">日記帳</t>
+          <t xml:space="preserve">最後の録音</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/mizuno_apart.diary.title</t>
+          <t xml:space="preserve">doc/mizuno_apart.recorder.body</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4295,19 +3984,19 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">水野の日記</t>
+          <t xml:space="preserve">@file:doc_mizuno_apart.recorder.body</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/mizuno_apart.diary.body</t>
+          <t xml:space="preserve">doc/mizuno_apart.toy.title</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc</t>
+          <t xml:space="preserve">toy</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4322,19 +4011,19 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:doc_mizuno_apart.diary.body</t>
+          <t xml:space="preserve">思い出の断片：髪のリボン</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/mizuno_apart.recorder.name</t>
+          <t xml:space="preserve">doc/mizuno_apart.toy.body</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc</t>
+          <t xml:space="preserve">toy</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4349,19 +4038,19 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">ボイスレコーダー</t>
+          <t xml:space="preserve">@file:doc_mizuno_apart.toy.body</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/mizuno_apart.recorder.title</t>
+          <t xml:space="preserve">echo/mizuno_uncle.title</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc</t>
+          <t xml:space="preserve">echo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4376,19 +4065,19 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">最後の録音</t>
+          <t xml:space="preserve">残響：病室（幼い水野の記憶）</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/mizuno_apart.recorder.body</t>
+          <t xml:space="preserve">echo/mizuno_uncle.body</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc</t>
+          <t xml:space="preserve">echo</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4403,19 +4092,19 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:doc_mizuno_apart.recorder.body</t>
+          <t xml:space="preserve">@file:echo_mizuno_uncle.body</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/mizuno_apart.toy.name</t>
+          <t xml:space="preserve">echo/talk_mizuno.title</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">echo</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4430,19 +4119,19 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">髪のリボン</t>
+          <t xml:space="preserve">残響：会話（水野の記憶）</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/mizuno_apart.toy.title</t>
+          <t xml:space="preserve">echo/talk_mizuno.body</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">echo</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4457,19 +4146,19 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">思い出の断片：髪のリボン</t>
+          <t xml:space="preserve">@file:echo_talk_mizuno.body</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/mizuno_apart.toy.body</t>
+          <t xml:space="preserve">lock/mizuno_apart.pcfile.name</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">lock</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4484,19 +4173,19 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:doc_mizuno_apart.toy.body</t>
+          <t xml:space="preserve">水野のノートPC</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/mizuno_apart.toy.hint</t>
+          <t xml:space="preserve">lock/mizuno_apart.pcfile.success_title</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">lock</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4511,19 +4200,19 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">娘の記憶</t>
+          <t xml:space="preserve">水野のPC：第12研究室 入室情報</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">echo/mizuno_uncle.title</t>
+          <t xml:space="preserve">lock/mizuno_apart.pcfile.success_body</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">echo</t>
+          <t xml:space="preserve">lock</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4538,19 +4227,19 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">残響：病室（幼い水野の記憶）</t>
+          <t xml:space="preserve">@file:lock_mizuno_apart.pcfile.success_body</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">echo/mizuno_uncle.body</t>
+          <t xml:space="preserve">lock/mizuno_apart.pcfile.require</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">echo</t>
+          <t xml:space="preserve">lock</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4565,19 +4254,19 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:echo_mizuno_uncle.body</t>
+          <t xml:space="preserve">まだ、必要なものが揃っていない。</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">echo/talk_mizuno.title</t>
+          <t xml:space="preserve">lock/mizuno_apart.pcfile.title</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">echo</t>
+          <t xml:space="preserve">lock</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4592,19 +4281,19 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">残響：会話（水野の記憶）</t>
+          <t xml:space="preserve">水野のノートPC</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">echo/talk_mizuno.body</t>
+          <t xml:space="preserve">lock/mizuno_apart.pcfile.body</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">echo</t>
+          <t xml:space="preserve">lock</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4618,168 +4307,6 @@
         </is>
       </c>
       <c r="G58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">@file:echo_talk_mizuno.body</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lock/mizuno_apart.pcfile.name</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lock</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mizuno_apart</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仮</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">水野のノートPC</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lock/mizuno_apart.pcfile.success_title</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lock</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mizuno_apart</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仮</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">水野のPC：第12研究室 入室情報</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lock/mizuno_apart.pcfile.success_body</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lock</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mizuno_apart</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仮</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">@file:lock_mizuno_apart.pcfile.success_body</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lock/mizuno_apart.pcfile.require</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lock</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mizuno_apart</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仮</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">まだ、必要なものが揃っていない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lock/mizuno_apart.pcfile.title</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lock</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mizuno_apart</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仮</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">水野のノートPC</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lock/mizuno_apart.pcfile.body</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lock</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mizuno_apart</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仮</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
         <is>
           <t xml:space="preserve">@file:lock_mizuno_apart.pcfile.body</t>
         </is>
@@ -4919,6 +4446,11 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">議事録</t>
@@ -5000,6 +4532,11 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">黒田のメモ</t>
@@ -5081,6 +4618,11 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">走り書き</t>
@@ -5144,7 +4686,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/data_room.toy.name</t>
+          <t xml:space="preserve">doc/data_room.toy.title</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5164,14 +4706,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">積み木の家</t>
+          <t xml:space="preserve">思い出の断片：積み木の家</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/data_room.toy.title</t>
+          <t xml:space="preserve">doc/data_room.toy.body</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5191,19 +4733,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">思い出の断片：積み木の家</t>
+          <t xml:space="preserve">@file:doc_data_room.toy.body</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/data_room.toy.body</t>
+          <t xml:space="preserve">echo/argue_kuroda.title</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">echo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -5218,19 +4760,19 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:doc_data_room.toy.body</t>
+          <t xml:space="preserve">残響：口論（黒田の記憶）</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/data_room.toy.hint</t>
+          <t xml:space="preserve">echo/argue_kuroda.body</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">echo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -5245,19 +4787,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">娘の記憶</t>
+          <t xml:space="preserve">@file:echo_argue_kuroda.body</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">echo/argue_kuroda.title</t>
+          <t xml:space="preserve">lock/data_room.audit.name</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">echo</t>
+          <t xml:space="preserve">lock</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5272,19 +4814,19 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">残響：口論（黒田の記憶）</t>
+          <t xml:space="preserve">入退室ログ端末</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">echo/argue_kuroda.body</t>
+          <t xml:space="preserve">lock/data_room.audit.success_title</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">echo</t>
+          <t xml:space="preserve">lock</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5299,14 +4841,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:echo_argue_kuroda.body</t>
+          <t xml:space="preserve">照合結果：主任IDの移動記録は本人ではない</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/data_room.audit.name</t>
+          <t xml:space="preserve">lock/data_room.audit.success_body</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5326,14 +4868,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">入退室ログ端末</t>
+          <t xml:space="preserve">@file:lock_data_room.audit.success_body</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/data_room.audit.success_title</t>
+          <t xml:space="preserve">lock/data_room.audit.require</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5353,14 +4895,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">照合結果：主任IDの移動記録は本人ではない</t>
+          <t xml:space="preserve">まだ、必要なものが揃っていない。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/data_room.audit.success_body</t>
+          <t xml:space="preserve">lock/data_room.audit.title</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5380,14 +4922,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:lock_data_room.audit.success_body</t>
+          <t xml:space="preserve">入退室ログ照合　4/16 〜 4/20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/data_room.audit.require</t>
+          <t xml:space="preserve">lock/data_room.audit.body</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5407,14 +4949,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">まだ、必要なものが揃っていない。</t>
+          <t xml:space="preserve">記録のうち「あり得ない行」を特定せよ。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/data_room.audit.title</t>
+          <t xml:space="preserve">lock/data_room.audit.row.0</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5434,14 +4976,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">入退室ログ照合　4/16 〜 4/20</t>
+          <t xml:space="preserve">04/16 09:02  黒田  第10研究室 入室</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/data_room.audit.body</t>
+          <t xml:space="preserve">lock/data_room.audit.row.1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5461,14 +5003,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">記録のうち「あり得ない行」を特定せよ。</t>
+          <t xml:space="preserve">04/16 13:40  水野  臨床病棟   入室</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/data_room.audit.row.0</t>
+          <t xml:space="preserve">lock/data_room.audit.row.2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5488,14 +5030,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">04/16 09:02  黒田  第10研究室 入室</t>
+          <t xml:space="preserve">04/17 22:15  佐伯  第8研究室  入室</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/data_room.audit.row.1</t>
+          <t xml:space="preserve">lock/data_room.audit.row.3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5515,14 +5057,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">04/16 13:40  水野  臨床病棟   入室</t>
+          <t xml:space="preserve">04/18 08:55  水野  臨床病棟   入室</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/data_room.audit.row.2</t>
+          <t xml:space="preserve">lock/data_room.audit.row.4</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5542,14 +5084,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">04/17 22:15  佐伯  第8研究室  入室</t>
+          <t xml:space="preserve">04/18 23:41  主任  第12研究室 入室</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/data_room.audit.row.3</t>
+          <t xml:space="preserve">lock/data_room.audit.row.5</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5569,14 +5111,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">04/18 08:55  水野  臨床病棟   入室</t>
+          <t xml:space="preserve">04/18 23:58  主任  第12研究室 退室</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/data_room.audit.row.4</t>
+          <t xml:space="preserve">lock/data_room.audit.row.6</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5596,14 +5138,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">04/18 23:41  主任  第12研究室 入室</t>
+          <t xml:space="preserve">04/19 00:12  主任  第12研究室 入室</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/data_room.audit.row.5</t>
+          <t xml:space="preserve">lock/data_room.audit.row.7</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5623,14 +5165,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">04/18 23:58  主任  第12研究室 退室</t>
+          <t xml:space="preserve">04/19 07:30  黒田  データ管理室 入室</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/data_room.audit.row.6</t>
+          <t xml:space="preserve">lock/data_room.audit.row.8</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5650,14 +5192,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">04/19 00:12  主任  第12研究室 入室</t>
+          <t xml:space="preserve">04/19 09:10  佐伯  第8研究室  入室</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/data_room.audit.row.7</t>
+          <t xml:space="preserve">lock/data_room.audit.row.9</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5677,24 +5219,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">04/19 07:30  黒田  データ管理室 入室</t>
+          <t xml:space="preserve">04/20 18:05  主任  第1研究室  入室</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/data_room.audit.row.8</t>
+          <t xml:space="preserve">room/system_room.name</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock</t>
+          <t xml:space="preserve">room</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">data_room</t>
+          <t xml:space="preserve">system_room</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -5704,24 +5246,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">04/19 09:10  佐伯  第8研究室  入室</t>
+          <t xml:space="preserve">SYSTEM ROOM</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/data_room.audit.row.9</t>
+          <t xml:space="preserve">room/system_room.chapter</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock</t>
+          <t xml:space="preserve">room</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">data_room</t>
+          <t xml:space="preserve">system_room</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -5731,19 +5273,19 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">04/20 18:05  主任  第1研究室  入室</t>
+          <t xml:space="preserve">3章『黒田恒一』　─ 転 ─</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">room/system_room.name</t>
+          <t xml:space="preserve">doc/system_room.devlog.name</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">room</t>
+          <t xml:space="preserve">doc</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5756,21 +5298,26 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">SYSTEM ROOM</t>
+          <t xml:space="preserve">開発記録</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">room/system_room.chapter</t>
+          <t xml:space="preserve">doc/system_room.devlog.title</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">room</t>
+          <t xml:space="preserve">doc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5785,14 +5332,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">3章『黒田恒一』　─ 転 ─</t>
+          <t xml:space="preserve">開発記録・治療手順</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/system_room.devlog.name</t>
+          <t xml:space="preserve">doc/system_room.devlog.body</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5812,14 +5359,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">開発記録</t>
+          <t xml:space="preserve">@file:doc_system_room.devlog.body</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/system_room.devlog.title</t>
+          <t xml:space="preserve">doc/system_room.gaplog.name</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5837,16 +5384,21 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">開発記録・治療手順</t>
+          <t xml:space="preserve">照合ログ</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/system_room.devlog.body</t>
+          <t xml:space="preserve">doc/system_room.gaplog.title</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5866,14 +5418,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:doc_system_room.devlog.body</t>
+          <t xml:space="preserve">黒田の照合ログ</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/system_room.gaplog.name</t>
+          <t xml:space="preserve">doc/system_room.gaplog.body</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5893,14 +5445,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">照合ログ</t>
+          <t xml:space="preserve">@file:doc_system_room.gaplog.body</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/system_room.gaplog.title</t>
+          <t xml:space="preserve">doc/system_room.restored.name</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5918,16 +5470,21 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">黒田の照合ログ</t>
+          <t xml:space="preserve">復元ファイル</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/system_room.gaplog.body</t>
+          <t xml:space="preserve">doc/system_room.restored.title</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5947,14 +5504,14 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:doc_system_room.gaplog.body</t>
+          <t xml:space="preserve">復元された操作記録</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/system_room.restored.name</t>
+          <t xml:space="preserve">doc/system_room.restored.body</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5974,19 +5531,19 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">復元ファイル</t>
+          <t xml:space="preserve">@file:doc_system_room.restored.body</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/system_room.restored.title</t>
+          <t xml:space="preserve">doc/system_room.toy.title</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc</t>
+          <t xml:space="preserve">toy</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6001,19 +5558,19 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">復元された操作記録</t>
+          <t xml:space="preserve">思い出の断片：おもちゃのカメラ</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/system_room.restored.body</t>
+          <t xml:space="preserve">doc/system_room.toy.body</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc</t>
+          <t xml:space="preserve">toy</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6028,24 +5585,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:doc_system_room.restored.body</t>
+          <t xml:space="preserve">@file:doc_system_room.toy.body</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/system_room.toy.name</t>
+          <t xml:space="preserve">room/kuroda_home.name</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">room</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">system_room</t>
+          <t xml:space="preserve">kuroda_home</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -6055,24 +5612,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">おもちゃのカメラ</t>
+          <t xml:space="preserve">黒田の自宅</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/system_room.toy.title</t>
+          <t xml:space="preserve">room/kuroda_home.chapter</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">room</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">system_room</t>
+          <t xml:space="preserve">kuroda_home</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -6082,24 +5639,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">思い出の断片：おもちゃのカメラ</t>
+          <t xml:space="preserve">3章『黒田恒一』　─ 結 ─</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/system_room.toy.body</t>
+          <t xml:space="preserve">doc/kuroda_home.drawing.name</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">doc</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">system_room</t>
+          <t xml:space="preserve">kuroda_home</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -6107,26 +5664,31 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:doc_system_room.toy.body</t>
+          <t xml:space="preserve">子供の絵</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/system_room.toy.hint</t>
+          <t xml:space="preserve">doc/kuroda_home.drawing.title</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">doc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">system_room</t>
+          <t xml:space="preserve">kuroda_home</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -6136,19 +5698,19 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">娘の記憶</t>
+          <t xml:space="preserve">冷蔵庫の絵</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">room/kuroda_home.name</t>
+          <t xml:space="preserve">doc/kuroda_home.drawing.body</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">room</t>
+          <t xml:space="preserve">doc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6163,19 +5725,19 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">黒田の自宅</t>
+          <t xml:space="preserve">@file:doc_kuroda_home.drawing.body</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">room/kuroda_home.chapter</t>
+          <t xml:space="preserve">doc/kuroda_home.rules.name</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">room</t>
+          <t xml:space="preserve">doc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -6188,16 +5750,21 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">3章『黒田恒一』　─ 結 ─</t>
+          <t xml:space="preserve">個人記録</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/kuroda_home.drawing.name</t>
+          <t xml:space="preserve">doc/kuroda_home.rules.title</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6217,14 +5784,14 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">子供の絵</t>
+          <t xml:space="preserve">黒田の個人記録</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/kuroda_home.drawing.title</t>
+          <t xml:space="preserve">doc/kuroda_home.rules.body</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6244,14 +5811,14 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">冷蔵庫の絵</t>
+          <t xml:space="preserve">@file:doc_kuroda_home.rules.body</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/kuroda_home.drawing.body</t>
+          <t xml:space="preserve">doc/kuroda_home.lastrec.name</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6269,16 +5836,21 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:doc_kuroda_home.drawing.body</t>
+          <t xml:space="preserve">対峙の記録</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/kuroda_home.rules.name</t>
+          <t xml:space="preserve">doc/kuroda_home.lastrec.title</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6298,14 +5870,14 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">個人記録</t>
+          <t xml:space="preserve">最後の対峙の記録（破損）</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/kuroda_home.rules.title</t>
+          <t xml:space="preserve">doc/kuroda_home.lastrec.body</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6325,19 +5897,19 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">黒田の個人記録</t>
+          <t xml:space="preserve">@file:doc_kuroda_home.lastrec.body</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/kuroda_home.rules.body</t>
+          <t xml:space="preserve">doc/kuroda_home.toy.title</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc</t>
+          <t xml:space="preserve">toy</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6352,19 +5924,19 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:doc_kuroda_home.rules.body</t>
+          <t xml:space="preserve">思い出の断片：折れた赤いクレヨン</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/kuroda_home.lastrec.name</t>
+          <t xml:space="preserve">doc/kuroda_home.toy.body</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc</t>
+          <t xml:space="preserve">toy</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6379,19 +5951,19 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">対峙の記録</t>
+          <t xml:space="preserve">@file:doc_kuroda_home.toy.body</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/kuroda_home.lastrec.title</t>
+          <t xml:space="preserve">echo/kuroda_family.title</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc</t>
+          <t xml:space="preserve">echo</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6406,19 +5978,19 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">最後の対峙の記録（破損）</t>
+          <t xml:space="preserve">残響：食卓（黒田の家族の記憶）</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/kuroda_home.lastrec.body</t>
+          <t xml:space="preserve">echo/kuroda_family.body</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc</t>
+          <t xml:space="preserve">echo</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -6433,19 +6005,19 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:doc_kuroda_home.lastrec.body</t>
+          <t xml:space="preserve">@file:echo_kuroda_family.body</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/kuroda_home.toy.name</t>
+          <t xml:space="preserve">lock/kuroda_home.verdict.name</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">lock</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6460,19 +6032,19 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">折れた赤いクレヨン</t>
+          <t xml:space="preserve">黒田の手帳（白紙のページ）</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/kuroda_home.toy.title</t>
+          <t xml:space="preserve">lock/kuroda_home.verdict.success_title</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">lock</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -6487,19 +6059,19 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">思い出の断片：折れた赤いクレヨン</t>
+          <t xml:space="preserve">判定：どちらも、怒鳴ってはいなかった</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/kuroda_home.toy.body</t>
+          <t xml:space="preserve">lock/kuroda_home.verdict.success_body</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">lock</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -6514,19 +6086,19 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:doc_kuroda_home.toy.body</t>
+          <t xml:space="preserve">@file:lock_kuroda_home.verdict.success_body</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/kuroda_home.toy.hint</t>
+          <t xml:space="preserve">lock/kuroda_home.verdict.require</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">lock</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -6541,19 +6113,19 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">娘の記憶</t>
+          <t xml:space="preserve">まだ、必要なものが揃っていない。</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">echo/kuroda_family.title</t>
+          <t xml:space="preserve">lock/kuroda_home.verdict.title</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">echo</t>
+          <t xml:space="preserve">lock</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -6568,19 +6140,19 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">残響：食卓（黒田の家族の記憶）</t>
+          <t xml:space="preserve">黒田の手帳　── 白紙のページ ──</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">echo/kuroda_family.body</t>
+          <t xml:space="preserve">lock/kuroda_home.verdict.body</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">echo</t>
+          <t xml:space="preserve">lock</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -6595,14 +6167,14 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:echo_kuroda_family.body</t>
+          <t xml:space="preserve">@file:lock_kuroda_home.verdict.body</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/kuroda_home.verdict.name</t>
+          <t xml:space="preserve">lock/kuroda_home.verdict.notenough</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6622,14 +6194,14 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">黒田の手帳（白紙のページ）</t>
+          <t xml:space="preserve">まだ判断できない。あの口論を、両方の側から見ていない。</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/kuroda_home.verdict.success_title</t>
+          <t xml:space="preserve">lock/kuroda_home.verdict.option.0</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6649,14 +6221,14 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">判定：どちらも、怒鳴ってはいなかった</t>
+          <t xml:space="preserve">佐伯</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/kuroda_home.verdict.success_body</t>
+          <t xml:space="preserve">lock/kuroda_home.verdict.option.1</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6676,14 +6248,14 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:lock_kuroda_home.verdict.success_body</t>
+          <t xml:space="preserve">黒田</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock/kuroda_home.verdict.require</t>
+          <t xml:space="preserve">lock/kuroda_home.verdict.option.2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6702,168 +6274,6 @@
         </is>
       </c>
       <c r="G70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">まだ、必要なものが揃っていない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lock/kuroda_home.verdict.title</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lock</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kuroda_home</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仮</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">黒田の手帳　── 白紙のページ ──</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lock/kuroda_home.verdict.body</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lock</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kuroda_home</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仮</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">@file:lock_kuroda_home.verdict.body</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lock/kuroda_home.verdict.notenough</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lock</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kuroda_home</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仮</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">まだ判断できない。あの口論を、両方の側から見ていない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lock/kuroda_home.verdict.option.0</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lock</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kuroda_home</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仮</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">佐伯</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lock/kuroda_home.verdict.option.1</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lock</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kuroda_home</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仮</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">黒田</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lock/kuroda_home.verdict.option.2</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lock</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kuroda_home</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仮</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
         <is>
           <t xml:space="preserve">どちらでもない──記憶は主観で歪む</t>
         </is>
@@ -7003,6 +6413,11 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">操作端末</t>
@@ -7066,7 +6481,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/core_main.toy.name</t>
+          <t xml:space="preserve">doc/core_main.toy.title</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -7086,14 +6501,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">小さな靴（片方）</t>
+          <t xml:space="preserve">思い出の断片：小さな靴（片方）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/core_main.toy.title</t>
+          <t xml:space="preserve">doc/core_main.toy.body</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -7113,24 +6528,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">思い出の断片：小さな靴（片方）</t>
+          <t xml:space="preserve">@file:doc_core_main.toy.body</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/core_main.toy.body</t>
+          <t xml:space="preserve">room/son_room.name</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">room</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">core_main</t>
+          <t xml:space="preserve">son_room</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -7140,24 +6555,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">@file:doc_core_main.toy.body</t>
+          <t xml:space="preserve">息子の部屋</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/core_main.toy.hint</t>
+          <t xml:space="preserve">room/son_room.chapter</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">room</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">core_main</t>
+          <t xml:space="preserve">son_room</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -7167,19 +6582,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">娘の記憶</t>
+          <t xml:space="preserve">終章　─ 誰の記憶でもない部屋 ─</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">room/son_room.name</t>
+          <t xml:space="preserve">doc/son_room.plan.name</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">room</t>
+          <t xml:space="preserve">doc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -7192,21 +6607,26 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調べる時の表示名</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">息子の部屋</t>
+          <t xml:space="preserve">古いファイル</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">room/son_room.chapter</t>
+          <t xml:space="preserve">doc/son_room.plan.title</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">room</t>
+          <t xml:space="preserve">doc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -7221,14 +6641,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">終章　─ 誰の記憶でもない部屋 ─</t>
+          <t xml:space="preserve">書きかけの治療計画書</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">doc/son_room.plan.name</t>
+          <t xml:space="preserve">doc/son_room.plan.body</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -7247,60 +6667,6 @@
         </is>
       </c>
       <c r="G13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">古いファイル</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">doc/son_room.plan.title</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">doc</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">son_room</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仮</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">書きかけの治療計画書</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">doc/son_room.plan.body</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">doc</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">son_room</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仮</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">@file:doc_son_room.plan.body</t>
         </is>
@@ -7368,12 +6734,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/pickup</t>
+          <t xml:space="preserve">doc/dim.flashlight.name</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">doc</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dim</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -7381,21 +6752,31 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トーストの品名</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">『{0}』を手に入れた{1}</t>
+          <t xml:space="preserve">懐中電灯</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/filed</t>
+          <t xml:space="preserve">doc/dim.flashlight.hint</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">doc</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dim</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -7403,21 +6784,31 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トーストの操作ヒント</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">『{0}』を手帳に綴じた</t>
+          <t xml:space="preserve">F: 点灯</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/echo_seen</t>
+          <t xml:space="preserve">doc/dim.notebook.name</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">doc</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dim</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -7425,21 +6816,31 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トーストの品名</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">残響を見た──『{0}』を手帳に記録した</t>
+          <t xml:space="preserve">手帳</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/need_notebook</t>
+          <t xml:space="preserve">doc/dim.notebook.hint</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">doc</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dim</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -7447,21 +6848,31 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トーストの操作ヒント</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">書き留めるものがない……手帳を探そう</t>
+          <t xml:space="preserve">Tab: 開く</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/prompt.doc</t>
+          <t xml:space="preserve">doc/dim.toy.name</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">toy</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dim</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -7469,21 +6880,31 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トーストの品名</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">[E] {0}を調べる</t>
+          <t xml:space="preserve">木のガラガラ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/prompt.doc_done</t>
+          <t xml:space="preserve">doc/dim.toy.hint</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">toy</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dim</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -7491,21 +6912,31 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トーストの操作ヒント</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">[E] {0}（記録済み）</t>
+          <t xml:space="preserve">娘の記憶</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/prompt.no_notebook</t>
+          <t xml:space="preserve">doc/train.toy.name</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">toy</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">train</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -7513,21 +6944,31 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トーストの品名</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">{0}（書き留めるものがない）</t>
+          <t xml:space="preserve">うさぎのぬいぐるみ</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/prompt.lock</t>
+          <t xml:space="preserve">doc/train.toy.hint</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">toy</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">train</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -7535,21 +6976,31 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トーストの操作ヒント</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">[E] {0}を操作する</t>
+          <t xml:space="preserve">娘の記憶</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/prompt.lock_done</t>
+          <t xml:space="preserve">doc/lab.toy.name</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">toy</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lab</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -7557,21 +7008,31 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トーストの品名</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">[E] {0}（解決済み）</t>
+          <t xml:space="preserve">折り紙の鶴</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/lock_done</t>
+          <t xml:space="preserve">doc/lab.toy.hint</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">toy</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lab</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -7579,21 +7040,31 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トーストの操作ヒント</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">{0}（解決済み）</t>
+          <t xml:space="preserve">娘の記憶</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/lock_solved</t>
+          <t xml:space="preserve">doc/study.toy.name</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">toy</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">study</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -7601,21 +7072,31 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トーストの品名</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{0}を解いた</t>
+          <t xml:space="preserve">絵本『おやすみ』</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/wrong</t>
+          <t xml:space="preserve">doc/study.toy.hint</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">toy</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">study</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -7623,21 +7104,31 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トーストの操作ヒント</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">違うようだ。</t>
+          <t xml:space="preserve">娘の記憶</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/wrong.flagged</t>
+          <t xml:space="preserve">doc/analysis.toy.name</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">toy</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">analysis</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -7645,21 +7136,31 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トーストの品名</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">　──手帳に付箋を立てた。関係のある記録があるはずだ</t>
+          <t xml:space="preserve">おもちゃの聴診器</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/wrong.reread</t>
+          <t xml:space="preserve">doc/analysis.toy.hint</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">toy</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">analysis</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7667,21 +7168,31 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トーストの操作ヒント</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">　──手帳の付箋を読み直そう</t>
+          <t xml:space="preserve">娘の記憶</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/wrong.unread</t>
+          <t xml:space="preserve">doc/saeki_home.toy.name</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">toy</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">saeki_home</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7689,29 +7200,923 @@
           <t xml:space="preserve">仮</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トーストの品名</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">　──まだ読んでいない資料があるのかもしれない</t>
+          <t xml:space="preserve">ままごとのカップ</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t xml:space="preserve">doc/saeki_home.toy.hint</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toy</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">saeki_home</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仮</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トーストの操作ヒント</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">娘の記憶</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doc/ward.toy.name</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toy</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ward</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仮</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トーストの品名</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">紙の王冠</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doc/ward.toy.hint</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toy</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ward</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仮</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トーストの操作ヒント</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">娘の記憶</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doc/core_ante.toy.name</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toy</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">core_ante</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仮</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トーストの品名</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビー玉</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doc/core_ante.toy.hint</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toy</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">core_ante</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仮</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トーストの操作ヒント</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">娘の記憶</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doc/mizuno_apart.toy.name</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toy</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mizuno_apart</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仮</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トーストの品名</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">髪のリボン</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doc/mizuno_apart.toy.hint</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toy</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mizuno_apart</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仮</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トーストの操作ヒント</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">娘の記憶</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doc/data_room.toy.name</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toy</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">data_room</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仮</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トーストの品名</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">積み木の家</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doc/data_room.toy.hint</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toy</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">data_room</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仮</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トーストの操作ヒント</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">娘の記憶</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doc/system_room.toy.name</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toy</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">system_room</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仮</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トーストの品名</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">おもちゃのカメラ</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doc/system_room.toy.hint</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toy</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">system_room</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仮</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トーストの操作ヒント</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">娘の記憶</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doc/kuroda_home.toy.name</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toy</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kuroda_home</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仮</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トーストの品名</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">折れた赤いクレヨン</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doc/kuroda_home.toy.hint</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toy</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kuroda_home</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仮</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トーストの操作ヒント</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">娘の記憶</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doc/core_main.toy.name</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toy</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">core_main</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仮</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トーストの品名</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">小さな靴（片方）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doc/core_main.toy.hint</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toy</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">core_main</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仮</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トーストの操作ヒント</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">娘の記憶</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/pickup</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仮</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">拾った時のトースト（{0}=品名 {1}=ヒント）</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">『{0}』を手に入れた{1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/filed</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仮</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">資料を読んだ時のトースト（{0}=見出し）</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">『{0}』を手帳に綴じた</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/need_notebook</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仮</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">手帳を持たずに資料を調べた時</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">書き留めるものがない……手帳を探そう</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/prompt.doc</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仮</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">拾う/調べる時の操作表示（{0}=品名）</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[E] {0}を調べる</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="7" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="5" max="5" width="7" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="52" customWidth="1"/>
+    <col min="8" max="8" width="52" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kind</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">room</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">speaker</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">note</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">en</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/echo_seen</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仮</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">残響を見た──『{0}』を手帳に記録した</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/prompt.doc_done</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仮</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[E] {0}（記録済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/prompt.no_notebook</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仮</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{0}（書き留めるものがない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/prompt.lock</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仮</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[E] {0}を操作する</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/prompt.lock_done</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仮</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[E] {0}（解決済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/lock_done</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仮</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{0}（解決済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/lock_solved</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仮</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{0}を解いた</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/wrong</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仮</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">違うようだ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/wrong.flagged</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仮</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　──手帳に付箋を立てた。関係のある記録があるはずだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/wrong.reread</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仮</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　──手帳の付箋を読み直そう</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/wrong.unread</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仮</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　──まだ読んでいない資料があるのかもしれない</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t xml:space="preserve">ui/step_of</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t xml:space="preserve">ui</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仮</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仮</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">@file:ui_step_of</t>
         </is>

--- a/進行/テキスト/GameText.xlsx
+++ b/進行/テキスト/GameText.xlsx
@@ -410,7 +410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1278,6 +1278,43 @@
       <c r="G29" t="inlineStr">
         <is>
           <t>@file:doc_lab.members.comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>doc/dim.tapeplayer.comment</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>doc</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>dim</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>二宮</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>仮</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>主人公のひと言（字幕）</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>@file:doc_dim.tapeplayer.comment</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4110,6 @@
           <t>saeki_home</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>仮</t>
@@ -6269,7 +6305,6 @@
           <t>mizuno_apart</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>仮</t>
@@ -6339,7 +6374,6 @@
           <t>mizuno_apart</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>仮</t>
@@ -9039,7 +9073,6 @@
           <t>kuroda_home</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>仮</t>
@@ -9109,7 +9142,6 @@
           <t>kuroda_home</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>仮</t>
@@ -9206,7 +9238,6 @@
           <t>kuroda_home</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>仮</t>
@@ -10115,7 +10146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -11235,6 +11266,70 @@
       <c r="G35" t="inlineStr">
         <is>
           <t>[E] {0}を調べる</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>doc/dim.tapeplayer.name</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>doc</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>dim</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>仮</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>トーストの品名</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>カセットレコーダー</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>doc/dim.tapeplayer.hint</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>doc</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>dim</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>仮</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>トーストの操作ヒント</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>カセットテープを聞ける</t>
         </is>
       </c>
     </row>

--- a/進行/テキスト/GameText.xlsx
+++ b/進行/テキスト/GameText.xlsx
@@ -1151,7 +1151,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1章『佐伯恒一』　─ 起 ─</t>
+          <t>1章『松原 翼』　─ 起 ─</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>残響：主任と佐伯の密談（私の記憶）</t>
+          <t>残響：主任と松原の密談（私の記憶）</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1章『佐伯恒一』　─ 転 ─</t>
+          <t>1章『松原 翼』　─ 転 ─</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>ヘルメット型スキャン装置</t>
+          <t>記憶転送用ヘルメット</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>ヘルメット型スキャン装置</t>
+          <t>記憶転送用ヘルメット　取扱説明</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>職員証（佐伯恒一）</t>
+          <t>職員証（松原 翼）</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>アルゴリズム仕様</t>
+          <t>アルゴリズム仕様書</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>補完アルゴリズム仕様（佐伯）</t>
+          <t>記憶補完アルゴリズム仕様書</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>異常レポート</t>
+          <t>異常報告</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>異常レポート（佐伯→所長）</t>
+          <t>記憶抽出試験における異常報告</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>佐伯の自宅</t>
+          <t>松原の自宅</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1章『佐伯恒一』　─ 結 ─</t>
+          <t>1章『松原 翼』　─ 結 ─</t>
         </is>
       </c>
     </row>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>佐伯の私的ログ（最終頁）</t>
+          <t>松原の私的ログ（最終頁）</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>残響：口論（佐伯の記憶）</t>
+          <t>残響：口論（松原の記憶）</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>補完試験 口述 No.12　佐伯</t>
+          <t>補完試験 口述 No.12　松原</t>
         </is>
       </c>
     </row>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>佐伯</t>
+          <t>松原</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>補完試験、第12回。記録、佐伯。</t>
+          <t>補完試験、第12回。記録、松原。</t>
         </is>
       </c>
     </row>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>佐伯</t>
+          <t>松原</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>佐伯</t>
+          <t>松原</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>佐伯さん。その補完に使う脳情報は、何人分あれば足りるんですか。</t>
+          <t>松原さん。その補完に使う脳情報は、何人分あれば足りるんですか。</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>佐伯</t>
+          <t>松原</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>……二宮さん。録音中です。</t>
+          <t>……久賀さん。録音中です。</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>佐伯</t>
+          <t>松原</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>佐伯</t>
+          <t>松原</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>佐伯</t>
+          <t>松原</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>佐伯</t>
+          <t>松原</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2章『水野美奈』　─ 起 ─</t>
+          <t>2章『川崎 千咲都』　─ 起 ─</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>水野の患者観察記録</t>
+          <t>川崎の患者観察記録</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2章『水野美奈』　─ 転 ─</t>
+          <t>2章『川崎 千咲都』　─ 転 ─</t>
         </is>
       </c>
     </row>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>水野の発見メモ</t>
+          <t>川崎の発見メモ</t>
         </is>
       </c>
     </row>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>未送信メッセージ（水野）</t>
+          <t>未送信メッセージ（川崎）</t>
         </is>
       </c>
     </row>
@@ -5355,7 +5355,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>水野のアパート</t>
+          <t>川崎のアパート</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2章『水野美奈』　─ 結 ─</t>
+          <t>2章『川崎 千咲都』　─ 結 ─</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>水野の日記</t>
+          <t>川崎の日記</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>残響：病室（幼い水野の記憶）</t>
+          <t>残響：病室（幼い川崎の記憶）</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>残響：会話（水野の記憶）</t>
+          <t>残響：会話（川崎の記憶）</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>水野のノートPC</t>
+          <t>川崎のノートPC</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>水野のPC：第12研究室 入室情報</t>
+          <t>川崎のPC：第12研究室 入室情報</t>
         </is>
       </c>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>水野のノートPC</t>
+          <t>川崎のノートPC</t>
         </is>
       </c>
     </row>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>水野</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>佐伯さん、電話に出ない。黒田さんも会議中。主任も出ない。</t>
+          <t>松原さん、電話に出ない。海尾さんも会議中。主任も出ない。</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>水野</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>水野</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>面会用　二宮さん　No.31</t>
+          <t>面会用　久賀さん　No.31</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>水野</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -6598,7 +6598,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>二宮さん。いま、目が動きました。お父さんの声のときだけ、動くんです。</t>
+          <t>久賀さん。いま、目が動きました。お父さんの声のときだけ、動くんです。</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3章『黒田恒一』　─ 起 ─</t>
+          <t>3章『海尾 諒多郎』　─ 起 ─</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>黒田のメモ</t>
+          <t>海尾のメモ</t>
         </is>
       </c>
     </row>
@@ -6900,7 +6900,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>黒田のメモ（一部欠損）</t>
+          <t>海尾のメモ（一部欠損）</t>
         </is>
       </c>
     </row>
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>残響：口論（黒田の記憶）</t>
+          <t>残響：口論（海尾の記憶）</t>
         </is>
       </c>
     </row>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>04/16 09:02  黒田  第10研究室 入室</t>
+          <t>04/16 09:02  海尾  第10研究室 入室</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>04/16 13:40  水野  臨床病棟   入室</t>
+          <t>04/16 13:40  川崎  臨床病棟   入室</t>
         </is>
       </c>
     </row>
@@ -7364,7 +7364,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>04/17 22:15  佐伯  第8研究室  入室</t>
+          <t>04/17 22:15  松原  第8研究室  入室</t>
         </is>
       </c>
     </row>
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>04/18 08:55  水野  臨床病棟   入室</t>
+          <t>04/18 08:55  川崎  臨床病棟   入室</t>
         </is>
       </c>
     </row>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>04/19 07:30  黒田  データ管理室 入室</t>
+          <t>04/19 07:30  海尾  データ管理室 入室</t>
         </is>
       </c>
     </row>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>04/19 09:10  佐伯  第8研究室  入室</t>
+          <t>04/19 09:10  松原  第8研究室  入室</t>
         </is>
       </c>
     </row>
@@ -7607,7 +7607,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>3章『黒田恒一』　─ 転 ─</t>
+          <t>3章『海尾 諒多郎』　─ 転 ─</t>
         </is>
       </c>
     </row>
@@ -7752,7 +7752,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>黒田の照合ログ</t>
+          <t>海尾の照合ログ</t>
         </is>
       </c>
     </row>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>黒田の自宅</t>
+          <t>海尾の自宅</t>
         </is>
       </c>
     </row>
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>3章『黒田恒一』　─ 結 ─</t>
+          <t>3章『海尾 諒多郎』　─ 結 ─</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>黒田の個人記録</t>
+          <t>海尾の個人記録</t>
         </is>
       </c>
     </row>
@@ -8312,7 +8312,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>残響：食卓（黒田の家族の記憶）</t>
+          <t>残響：食卓（海尾の家族の記憶）</t>
         </is>
       </c>
     </row>
@@ -8366,7 +8366,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>黒田の手帳（白紙のページ）</t>
+          <t>海尾の手帳（白紙のページ）</t>
         </is>
       </c>
     </row>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>黒田の手帳　── 白紙のページ ──</t>
+          <t>海尾の手帳　── 白紙のページ ──</t>
         </is>
       </c>
     </row>
@@ -8555,7 +8555,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>佐伯</t>
+          <t>松原</t>
         </is>
       </c>
     </row>
@@ -8582,7 +8582,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>黒田</t>
+          <t>海尾</t>
         </is>
       </c>
     </row>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -8705,7 +8705,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -8927,7 +8927,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8964,7 +8964,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>黒田</t>
+          <t>海尾</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>黒田</t>
+          <t>海尾</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>黒田</t>
+          <t>海尾</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>黒田</t>
+          <t>海尾</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>黒田</t>
+          <t>海尾</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>黒田</t>
+          <t>海尾</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9540,7 +9540,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>再生メッセージ　小川 暁</t>
+          <t>再生メッセージ　三木 宗英</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>二宮</t>
+          <t>久賀</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -9857,7 +9857,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>小川</t>
+          <t>三木</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -9872,7 +9872,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>二宮さん。ここまで来たなら、もう思い出しましたね。</t>
+          <t>久賀さん。ここまで来たなら、もう思い出しましたね。</t>
         </is>
       </c>
     </row>
@@ -9894,7 +9894,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>小川</t>
+          <t>三木</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>小川</t>
+          <t>三木</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>小川</t>
+          <t>三木</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -10005,7 +10005,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>小川</t>
+          <t>三木</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -10042,7 +10042,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>小川</t>
+          <t>三木</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10079,7 +10079,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>小川</t>
+          <t>三木</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>小川</t>
+          <t>三木</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">

--- a/進行/テキスト/GameText.xlsx
+++ b/進行/テキスト/GameText.xlsx
@@ -10057,7 +10057,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>その回廊も部屋も、リナシータがあなたと3人の記憶から作った空間です。私は彼らを消さない。それが私の償いです。</t>
+          <t>その回廊は、あなたがリナシータと共鳴した時に、あなたの頭の中に生まれたものです。部屋は、あなたと3人の記憶です。私は彼らを消さない。それが私の償いです。</t>
         </is>
       </c>
     </row>
